--- a/Funding/4_endproduct/v3/endproduct_v3_claude-sonnet-4-6_results.xlsx
+++ b/Funding/4_endproduct/v3/endproduct_v3_claude-sonnet-4-6_results.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="666" uniqueCount="341">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t xml:space="preserve">row_jaccard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notes</t>
   </si>
   <si>
     <t xml:space="preserve">A Revolutionary Tech for Exceptionally Efficient Natural  Muscle Tissue Growth in Cultivated Meat Applications</t>
@@ -549,6 +552,9 @@
   </si>
   <si>
     <t xml:space="preserve">The grant explicitly targets cultivated octopus meat as a seafood product, with the methodology described as applicable to the broader cultivated meat and seafood industries, warranting both Meat and Fish and seafood classifications.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Disagree. The product is octopus so it should be seafood only.</t>
   </si>
   <si>
     <t xml:space="preserve">Innovative patented dry fermentation technology for cost-effective and highly nutritious production of hybrid mycelium-plant meat analogues</t>
@@ -880,6 +886,9 @@
     <t xml:space="preserve">The grant explicitly targets mycelium-based whole cuts starting with fish and seafood analogues, and also references whole cuts of 'any kind,' which encompasses meat analogues, so both Meat and Fish and seafood are flagged true.</t>
   </si>
   <si>
+    <t xml:space="preserve">Stick with the specific product in the grant – should be seafood only.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Plant-Based Proteins and Antioxidants in
   Hybrid Meat for Dysphagia</t>
   </si>
@@ -1041,6 +1050,9 @@
     <t xml:space="preserve">The grant investigates fungi/mycelium for tempeh-like products but does not explicitly target any specific end product category (meat analogue, dairy, etc.), focusing instead on characterizing mushroom strains for nutritional content, flavor, safety, and gut effects — making it agnostic.</t>
   </si>
   <si>
+    <t xml:space="preserve">If an alternative protein aims to replicate an existing plant-based alternative like tempeh, should it be Meat given that it was tempeh is typically seen to replace?</t>
+  </si>
+  <si>
     <t xml:space="preserve">Thermal Reaction Products of Ochratoxin A: Metabolism and Bioavailability</t>
   </si>
   <si>
@@ -1067,6 +1079,9 @@
   </si>
   <si>
     <t xml:space="preserve">The abstract describes a process for upcycling dairy side streams via microalgae into alternative protein and functional ingredients, but does not explicitly name any specific end food product application, making this Agnostic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title literally says dairy-alternative products, so it should be Dairy.</t>
   </si>
   <si>
     <t xml:space="preserve">Upcycling water from legume processing to meet high demand for plant-based food ingredients: Creating new opportunities for UK legumes</t>
@@ -1163,6 +1178,9 @@
   </si>
   <si>
     <t xml:space="preserve">The grant describes extraction, cultivation, and bioreactor development for seaweed-derived mycoprotein with no specific food product application named beyond generic 'food and feed applications,' making it Agnostic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Up-cycling of whey streams via microalgae into innovative fortified dairy and dairy-alternative products - Whey2blue</t>
   </si>
   <si>
     <t xml:space="preserve">n_true</t>
@@ -1301,7 +1319,7 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1324,6 +1342,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFF8000"/>
         <bgColor rgb="FFFF6600"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FF993300"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -1361,7 +1391,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1390,6 +1420,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1399,7 +1437,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1434,7 +1472,23 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFFF0000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFF8000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1683,8 +1737,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P84"/>
+  <dimension ref="A1:O94"/>
   <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="11.53"/>
+  </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
@@ -1726,28 +1783,31 @@
       <c r="M1" s="0" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="0" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
         <v>43</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J2" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -1768,25 +1828,25 @@
         <v>4</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F3" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="0" t="s">
-        <v>19</v>
-      </c>
       <c r="H3" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I3" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J3" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -1807,22 +1867,22 @@
         <v>73</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I4" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J4" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -1843,22 +1903,22 @@
         <v>36</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J5" s="3" t="b">
         <f aca="false">FALSE()</f>
@@ -1873,8 +1933,8 @@
       <c r="M5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="0" t="s">
-        <v>30</v>
+      <c r="N5" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1882,22 +1942,22 @@
         <v>75</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G6" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="G6" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="I6" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J6" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -1918,22 +1978,22 @@
         <v>44</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I7" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J7" s="3" t="b">
         <f aca="false">FALSE()</f>
@@ -1948,8 +2008,8 @@
       <c r="M7" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="0" t="s">
-        <v>30</v>
+      <c r="N7" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1957,22 +2017,22 @@
         <v>46</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F8" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="G8" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="I8" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J8" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -1993,22 +2053,22 @@
         <v>27</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I9" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J9" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2029,22 +2089,22 @@
         <v>5</v>
       </c>
       <c r="B10" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F10" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="G10" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="I10" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J10" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2065,22 +2125,22 @@
         <v>31</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D11" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I11" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J11" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2101,22 +2161,22 @@
         <v>48</v>
       </c>
       <c r="B12" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D12" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F12" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G12" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I12" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="J12" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2137,22 +2197,22 @@
         <v>30</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D13" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G13" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I13" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J13" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2173,22 +2233,22 @@
         <v>0</v>
       </c>
       <c r="B14" s="0" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D14" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F14" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G14" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I14" s="0" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J14" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2209,22 +2269,22 @@
         <v>53</v>
       </c>
       <c r="B15" s="0" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D15" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F15" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="G15" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="G15" s="0" t="s">
-        <v>62</v>
-      </c>
       <c r="I15" s="0" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J15" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2245,22 +2305,22 @@
         <v>23</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D16" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F16" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I16" s="0" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J16" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2281,22 +2341,22 @@
         <v>61</v>
       </c>
       <c r="B17" s="0" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D17" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F17" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I17" s="0" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="J17" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2317,22 +2377,22 @@
         <v>9</v>
       </c>
       <c r="B18" s="0" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D18" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F18" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G18" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I18" s="0" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J18" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2353,22 +2413,22 @@
         <v>76</v>
       </c>
       <c r="B19" s="0" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D19" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F19" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G19" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I19" s="0" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J19" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2389,22 +2449,22 @@
         <v>78</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D20" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F20" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G20" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I20" s="0" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J20" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2425,22 +2485,22 @@
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D21" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F21" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G21" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I21" s="0" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J21" s="4" t="b">
         <f aca="false">FALSE()</f>
@@ -2455,8 +2515,8 @@
       <c r="M21" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="O21" s="0" t="s">
-        <v>84</v>
+      <c r="N21" s="0" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="209" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2464,28 +2524,28 @@
         <v>15</v>
       </c>
       <c r="B22" s="0" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D22" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E22" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F22" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G22" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H22" s="0" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I22" s="0" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J22" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2506,28 +2566,28 @@
         <v>77</v>
       </c>
       <c r="B23" s="0" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D23" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E23" s="0" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F23" s="0" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G23" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H23" s="0" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I23" s="0" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J23" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2548,22 +2608,22 @@
         <v>63</v>
       </c>
       <c r="B24" s="0" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D24" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F24" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G24" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I24" s="0" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J24" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2584,28 +2644,28 @@
         <v>55</v>
       </c>
       <c r="B25" s="0" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D25" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E25" s="0" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F25" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G25" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H25" s="0" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I25" s="0" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J25" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2626,22 +2686,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="0" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D26" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F26" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G26" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I26" s="0" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J26" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2662,22 +2722,22 @@
         <v>72</v>
       </c>
       <c r="B27" s="0" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D27" s="0" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F27" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G27" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I27" s="0" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J27" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2698,22 +2758,22 @@
         <v>22</v>
       </c>
       <c r="B28" s="0" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D28" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F28" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="G28" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="G28" s="0" t="s">
-        <v>62</v>
-      </c>
       <c r="I28" s="0" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J28" s="3" t="b">
         <f aca="false">FALSE()</f>
@@ -2728,8 +2788,8 @@
       <c r="M28" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="O28" s="0" t="s">
-        <v>30</v>
+      <c r="N28" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2737,25 +2797,25 @@
         <v>54</v>
       </c>
       <c r="B29" s="0" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D29" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E29" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F29" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G29" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I29" s="0" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J29" s="3" t="b">
         <f aca="false">FALSE()</f>
@@ -2770,8 +2830,8 @@
       <c r="M29" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="O29" s="0" t="s">
-        <v>30</v>
+      <c r="N29" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="56" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2779,22 +2839,22 @@
         <v>38</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D30" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F30" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G30" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I30" s="0" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J30" s="3" t="b">
         <f aca="false">FALSE()</f>
@@ -2809,11 +2869,11 @@
       <c r="M30" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="O30" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="P30" s="5" t="s">
-        <v>125</v>
+      <c r="N30" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="56" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2821,22 +2881,22 @@
         <v>71</v>
       </c>
       <c r="B31" s="0" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D31" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F31" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G31" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I31" s="0" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J31" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2857,28 +2917,28 @@
         <v>11</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C32" s="0" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D32" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E32" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F32" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G32" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H32" s="0" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I32" s="0" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J32" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2899,22 +2959,22 @@
         <v>3</v>
       </c>
       <c r="B33" s="0" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D33" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F33" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G33" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I33" s="0" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J33" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2935,22 +2995,22 @@
         <v>16</v>
       </c>
       <c r="B34" s="0" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C34" s="0" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D34" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F34" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G34" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I34" s="0" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J34" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -2971,25 +3031,25 @@
         <v>45</v>
       </c>
       <c r="B35" s="0" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D35" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E35" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F35" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G35" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I35" s="0" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J35" s="6" t="b">
         <f aca="false">FALSE()</f>
@@ -3004,8 +3064,8 @@
       <c r="M35" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="O35" s="0" t="s">
-        <v>141</v>
+      <c r="N35" s="0" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3013,24 +3073,24 @@
         <v>79</v>
       </c>
       <c r="B36" s="0" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C36" s="0" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D36" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F36" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G36" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I36" s="0" t="s">
-        <v>144</v>
-      </c>
-      <c r="J36" s="1" t="b">
+        <v>145</v>
+      </c>
+      <c r="J36" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3042,6 +3102,9 @@
       </c>
       <c r="M36" s="0" t="n">
         <v>0.5</v>
+      </c>
+      <c r="N36" s="0" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="296.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3049,22 +3112,22 @@
         <v>49</v>
       </c>
       <c r="B37" s="0" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D37" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F37" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G37" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I37" s="0" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="J37" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3085,22 +3148,22 @@
         <v>13</v>
       </c>
       <c r="B38" s="0" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D38" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F38" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G38" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I38" s="0" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J38" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3121,22 +3184,22 @@
         <v>59</v>
       </c>
       <c r="B39" s="0" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D39" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F39" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G39" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I39" s="0" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J39" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3157,22 +3220,22 @@
         <v>81</v>
       </c>
       <c r="B40" s="0" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C40" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D40" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F40" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G40" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I40" s="0" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J40" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3193,22 +3256,22 @@
         <v>34</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D41" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F41" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G41" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I41" s="0" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="J41" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3229,28 +3292,28 @@
         <v>42</v>
       </c>
       <c r="B42" s="0" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C42" s="0" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D42" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E42" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F42" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G42" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H42" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I42" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J42" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3271,28 +3334,28 @@
         <v>68</v>
       </c>
       <c r="B43" s="0" t="s">
+        <v>166</v>
+      </c>
+      <c r="C43" s="0" t="s">
+        <v>163</v>
+      </c>
+      <c r="D43" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="E43" s="0" t="s">
         <v>164</v>
       </c>
-      <c r="C43" s="0" t="s">
-        <v>161</v>
-      </c>
-      <c r="D43" s="0" t="s">
-        <v>19</v>
-      </c>
-      <c r="E43" s="0" t="s">
-        <v>162</v>
-      </c>
       <c r="F43" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G43" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H43" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I43" s="0" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J43" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3313,25 +3376,25 @@
         <v>32</v>
       </c>
       <c r="B44" s="0" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D44" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F44" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G44" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H44" s="0" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="I44" s="0" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J44" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3352,24 +3415,24 @@
         <v>52</v>
       </c>
       <c r="B45" s="0" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D45" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F45" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G45" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I45" s="0" t="s">
-        <v>172</v>
-      </c>
-      <c r="J45" s="1" t="b">
+        <v>174</v>
+      </c>
+      <c r="J45" s="3" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3381,6 +3444,9 @@
       </c>
       <c r="M45" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="N45" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3388,22 +3454,22 @@
         <v>37</v>
       </c>
       <c r="B46" s="0" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C46" s="0" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D46" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F46" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G46" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I46" s="0" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J46" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3424,24 +3490,24 @@
         <v>57</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D47" s="0" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F47" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G47" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I47" s="0" t="s">
-        <v>179</v>
-      </c>
-      <c r="J47" s="1" t="b">
+        <v>181</v>
+      </c>
+      <c r="J47" s="3" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3453,6 +3519,9 @@
       </c>
       <c r="M47" s="0" t="n">
         <v>0.5</v>
+      </c>
+      <c r="N47" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3460,22 +3529,22 @@
         <v>20</v>
       </c>
       <c r="B48" s="0" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C48" s="0" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D48" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F48" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G48" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I48" s="0" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J48" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3496,22 +3565,22 @@
         <v>80</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C49" s="0" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D49" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F49" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G49" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I49" s="0" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J49" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3532,30 +3601,30 @@
         <v>82</v>
       </c>
       <c r="B50" s="0" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C50" s="0" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D50" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E50" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F50" s="0" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G50" s="0" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="H50" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I50" s="0" t="s">
-        <v>191</v>
-      </c>
-      <c r="J50" s="1" t="b">
+        <v>193</v>
+      </c>
+      <c r="J50" s="3" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3567,6 +3636,9 @@
       </c>
       <c r="M50" s="0" t="n">
         <v>0.25</v>
+      </c>
+      <c r="N50" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3574,25 +3646,25 @@
         <v>26</v>
       </c>
       <c r="B51" s="0" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C51" s="0" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D51" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F51" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="G51" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H51" s="0" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="I51" s="0" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="J51" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3613,22 +3685,22 @@
         <v>2</v>
       </c>
       <c r="B52" s="0" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C52" s="0" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D52" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F52" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G52" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I52" s="0" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J52" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3649,28 +3721,28 @@
         <v>66</v>
       </c>
       <c r="B53" s="0" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C53" s="0" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D53" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E53" s="0" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F53" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="G53" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H53" s="0" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="I53" s="0" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J53" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3691,22 +3763,22 @@
         <v>12</v>
       </c>
       <c r="B54" s="0" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C54" s="0" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D54" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F54" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G54" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I54" s="0" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="J54" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3727,22 +3799,22 @@
         <v>29</v>
       </c>
       <c r="B55" s="0" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D55" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F55" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G55" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I55" s="0" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J55" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3763,22 +3835,22 @@
         <v>50</v>
       </c>
       <c r="B56" s="0" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D56" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F56" s="0" t="s">
+        <v>64</v>
+      </c>
+      <c r="G56" s="0" t="s">
         <v>63</v>
       </c>
-      <c r="G56" s="0" t="s">
-        <v>62</v>
-      </c>
       <c r="I56" s="0" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J56" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3799,22 +3871,22 @@
         <v>7</v>
       </c>
       <c r="B57" s="0" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C57" s="0" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D57" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F57" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G57" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="G57" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="I57" s="0" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J57" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3835,22 +3907,22 @@
         <v>60</v>
       </c>
       <c r="B58" s="0" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C58" s="0" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D58" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F58" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G58" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I58" s="0" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J58" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3871,22 +3943,22 @@
         <v>17</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C59" s="0" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D59" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F59" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G59" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I59" s="0" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J59" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -3907,24 +3979,24 @@
         <v>28</v>
       </c>
       <c r="B60" s="0" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D60" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F60" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G60" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I60" s="0" t="s">
-        <v>224</v>
-      </c>
-      <c r="J60" s="1" t="b">
+        <v>226</v>
+      </c>
+      <c r="J60" s="3" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3936,6 +4008,9 @@
       </c>
       <c r="M60" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="N60" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="45.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3943,24 +4018,24 @@
         <v>1</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D61" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G61" s="0" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I61" s="0" t="s">
-        <v>227</v>
-      </c>
-      <c r="J61" s="1" t="b">
+        <v>229</v>
+      </c>
+      <c r="J61" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -3972,6 +4047,9 @@
       </c>
       <c r="M61" s="0" t="n">
         <v>0.5</v>
+      </c>
+      <c r="N61" s="0" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="45.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3979,22 +4057,22 @@
         <v>62</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D62" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F62" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G62" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I62" s="0" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="J62" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4015,28 +4093,28 @@
         <v>70</v>
       </c>
       <c r="B63" s="0" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D63" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E63" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F63" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G63" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H63" s="0" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I63" s="0" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="J63" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4057,22 +4135,22 @@
         <v>35</v>
       </c>
       <c r="B64" s="0" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="C64" s="0" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="D64" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F64" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G64" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I64" s="0" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J64" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4093,24 +4171,24 @@
         <v>69</v>
       </c>
       <c r="B65" s="0" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="D65" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F65" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="G65" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I65" s="0" t="s">
-        <v>240</v>
-      </c>
-      <c r="J65" s="1" t="b">
+        <v>243</v>
+      </c>
+      <c r="J65" s="3" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4122,6 +4200,9 @@
       </c>
       <c r="M65" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="N65" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="34.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4129,22 +4210,22 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C66" s="0" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D66" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F66" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G66" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I66" s="0" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="J66" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4165,22 +4246,22 @@
         <v>41</v>
       </c>
       <c r="B67" s="0" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="C67" s="0" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D67" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F67" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G67" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="G67" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="I67" s="0" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="J67" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4201,22 +4282,22 @@
         <v>33</v>
       </c>
       <c r="B68" s="0" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D68" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F68" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G68" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="G68" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="I68" s="0" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="J68" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4237,22 +4318,22 @@
         <v>40</v>
       </c>
       <c r="B69" s="0" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C69" s="0" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D69" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F69" s="0" t="s">
+        <v>35</v>
+      </c>
+      <c r="G69" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="G69" s="0" t="s">
-        <v>33</v>
-      </c>
       <c r="I69" s="0" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="J69" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4273,24 +4354,24 @@
         <v>10</v>
       </c>
       <c r="B70" s="0" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C70" s="0" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D70" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F70" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="G70" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I70" s="0" t="s">
-        <v>255</v>
-      </c>
-      <c r="J70" s="1" t="b">
+        <v>258</v>
+      </c>
+      <c r="J70" s="3" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4309,22 +4390,22 @@
         <v>18</v>
       </c>
       <c r="B71" s="0" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="D71" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F71" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G71" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I71" s="0" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="J71" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4345,22 +4426,22 @@
         <v>8</v>
       </c>
       <c r="B72" s="0" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D72" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F72" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G72" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I72" s="0" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="J72" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4381,22 +4462,22 @@
         <v>58</v>
       </c>
       <c r="B73" s="0" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C73" s="0" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="D73" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F73" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G73" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I73" s="0" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="J73" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4417,24 +4498,24 @@
         <v>21</v>
       </c>
       <c r="B74" s="0" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="D74" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F74" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G74" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I74" s="0" t="s">
-        <v>267</v>
-      </c>
-      <c r="J74" s="1" t="b">
+        <v>270</v>
+      </c>
+      <c r="J74" s="8" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4446,6 +4527,9 @@
       </c>
       <c r="M74" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="N74" s="5" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4453,22 +4537,22 @@
         <v>51</v>
       </c>
       <c r="B75" s="0" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C75" s="0" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F75" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G75" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I75" s="0" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="J75" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4489,22 +4573,22 @@
         <v>67</v>
       </c>
       <c r="B76" s="0" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C76" s="0" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="D76" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F76" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G76" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I76" s="0" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="J76" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4525,27 +4609,27 @@
         <v>65</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C77" s="0" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D77" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E77" s="0" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F77" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G77" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I77" s="0" t="s">
-        <v>276</v>
-      </c>
-      <c r="J77" s="1" t="b">
+        <v>280</v>
+      </c>
+      <c r="J77" s="7" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4557,6 +4641,9 @@
       </c>
       <c r="M77" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="N77" s="0" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="77.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4564,24 +4651,24 @@
         <v>74</v>
       </c>
       <c r="B78" s="0" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D78" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F78" s="0" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G78" s="0" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="I78" s="0" t="s">
-        <v>281</v>
-      </c>
-      <c r="J78" s="1" t="b">
+        <v>286</v>
+      </c>
+      <c r="J78" s="3" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4593,6 +4680,9 @@
       </c>
       <c r="M78" s="0" t="n">
         <v>0.5</v>
+      </c>
+      <c r="N78" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="165" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4600,24 +4690,24 @@
         <v>56</v>
       </c>
       <c r="B79" s="0" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="D79" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F79" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G79" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I79" s="0" t="s">
-        <v>284</v>
-      </c>
-      <c r="J79" s="1" t="b">
+        <v>289</v>
+      </c>
+      <c r="J79" s="3" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4629,6 +4719,9 @@
       </c>
       <c r="M79" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="N79" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4636,28 +4729,28 @@
         <v>19</v>
       </c>
       <c r="B80" s="0" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C80" s="0" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="D80" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E80" s="0" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F80" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="G80" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="G80" s="0" t="s">
-        <v>19</v>
-      </c>
       <c r="H80" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I80" s="0" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="J80" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4678,22 +4771,22 @@
         <v>24</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C81" s="0" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D81" s="0" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F81" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G81" s="0" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I81" s="0" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="J81" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4714,22 +4807,22 @@
         <v>39</v>
       </c>
       <c r="B82" s="0" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="D82" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F82" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G82" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I82" s="0" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="J82" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4750,27 +4843,27 @@
         <v>47</v>
       </c>
       <c r="B83" s="0" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C83" s="0" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D83" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E83" s="0" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="F83" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="G83" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="I83" s="0" t="s">
-        <v>296</v>
-      </c>
-      <c r="J83" s="1" t="b">
+        <v>301</v>
+      </c>
+      <c r="J83" s="3" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
@@ -4782,6 +4875,9 @@
       </c>
       <c r="M83" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="N83" s="0" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="165" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4789,22 +4885,22 @@
         <v>14</v>
       </c>
       <c r="B84" s="0" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="D84" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F84" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G84" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I84" s="0" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="J84" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -4818,6 +4914,246 @@
       </c>
       <c r="M84" s="0" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B89" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C89" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D89" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F89" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="G89" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="H89" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="I89" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="J89" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="K89" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L89" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="M89" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="N89" s="0" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="88.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="B90" s="0" t="s">
+        <v>139</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D90" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="E90" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="F90" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G90" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="I90" s="0" t="s">
+        <v>141</v>
+      </c>
+      <c r="J90" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K90" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M90" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N90" s="0" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="0" t="n">
+        <v>79</v>
+      </c>
+      <c r="B91" s="0" t="s">
+        <v>143</v>
+      </c>
+      <c r="C91" s="0" t="s">
+        <v>144</v>
+      </c>
+      <c r="D91" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F91" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="G91" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="I91" s="0" t="s">
+        <v>145</v>
+      </c>
+      <c r="J91" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K91" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L91" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M91" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N91" s="0" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="45.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D92" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="F92" s="0" t="s">
+        <v>113</v>
+      </c>
+      <c r="G92" s="0" t="s">
+        <v>114</v>
+      </c>
+      <c r="I92" s="0" t="s">
+        <v>229</v>
+      </c>
+      <c r="J92" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K92" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L92" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" s="0" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N92" s="0" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="56" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B93" s="0" t="s">
+        <v>268</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="D93" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="F93" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G93" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="I93" s="0" t="s">
+        <v>270</v>
+      </c>
+      <c r="J93" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K93" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M93" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N93" s="5" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="23.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="0" t="n">
+        <v>65</v>
+      </c>
+      <c r="B94" s="0" t="s">
+        <v>305</v>
+      </c>
+      <c r="C94" s="0" t="s">
+        <v>279</v>
+      </c>
+      <c r="D94" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="E94" s="0" t="s">
+        <v>121</v>
+      </c>
+      <c r="F94" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="G94" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="I94" s="0" t="s">
+        <v>280</v>
+      </c>
+      <c r="J94" s="7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K94" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M94" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="0" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -4844,27 +5180,27 @@
         <v>3</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>20</v>
@@ -4879,15 +5215,15 @@
         <v>1</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>2</v>
@@ -4902,15 +5238,15 @@
         <v>2</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>20</v>
@@ -4925,15 +5261,15 @@
         <v>4</v>
       </c>
       <c r="F4" s="0" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>4</v>
@@ -4948,15 +5284,15 @@
         <v>1</v>
       </c>
       <c r="F5" s="0" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>0</v>
@@ -4971,15 +5307,15 @@
         <v>0</v>
       </c>
       <c r="F6" s="0" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G6" s="0" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>31</v>
@@ -4994,15 +5330,15 @@
         <v>6</v>
       </c>
       <c r="F7" s="0" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="G7" s="0" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>11</v>
@@ -5017,15 +5353,15 @@
         <v>1</v>
       </c>
       <c r="F8" s="0" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="G8" s="0" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>0</v>
@@ -5040,15 +5376,15 @@
         <v>0</v>
       </c>
       <c r="F9" s="0" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G9" s="0" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>0</v>
@@ -5063,15 +5399,15 @@
         <v>0</v>
       </c>
       <c r="F10" s="0" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G10" s="0" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>0</v>
@@ -5086,10 +5422,10 @@
         <v>0</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="G11" s="0" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -5113,21 +5449,21 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>83</v>
@@ -5135,10 +5471,10 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C3" s="0" t="n">
         <v>83</v>
@@ -5146,10 +5482,10 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="C4" s="0" t="n">
         <v>83</v>
@@ -5157,10 +5493,10 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="C5" s="0" t="n">
         <v>83</v>
@@ -5168,10 +5504,10 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="C6" s="0" t="n">
         <v>20</v>
@@ -5179,10 +5515,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C7" s="0" t="n">
         <v>20</v>
@@ -5190,10 +5526,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="C8" s="0" t="n">
         <v>20</v>
@@ -5201,10 +5537,10 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="C9" s="0" t="n">
         <v>20</v>
